--- a/tests/appium/results/appium-e2e-results.xlsx
+++ b/tests/appium/results/appium-e2e-results.xlsx
@@ -42,11 +42,11 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t xml:space="preserve">[init({"platformName":"Android","automationName":"UiAutomator2","deviceName":"Android Emulator","newCommandTimeout":240,"browserName":"Chrome"})] The environment you requested was unavailable.
-The requested resource could not be found, or a request was received using an HTTP method that is not supported by the mapped resource</t>
-  </si>
-  <si>
-    <t>2026-06-12T09:08:49.242Z</t>
+    <t xml:space="preserve">[init({"platformName":"Android","automationName":"UiAutomator2","udid":"ZSPFVGOBQKMBBMVO","newCommandTimeout":240,"goog:chromeOptions":{"w3c":false,"androidPackage":"com.android.chrome"},"browserName":"Chrome"})] The environment you requested was unavailable.
+The requested resource could not be found, or a request was received using an HTTP method that is not supported by the mapped resource.</t>
+  </si>
+  <si>
+    <t>2026-06-13T06:57:14.710Z</t>
   </si>
   <si>
     <t>Metric</t>
@@ -76,7 +76,7 @@
     <t>Execution Time</t>
   </si>
   <si>
-    <t>2026-06-12T09:08:49.260Z</t>
+    <t>2026-06-13T06:57:14.725Z</t>
   </si>
   <si>
     <t>Total</t>
